--- a/Aon_DCF_Model_v3.xlsx
+++ b/Aon_DCF_Model_v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arund\Downloads\Aon DCF Valuation - Github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arund\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CD98F0-1504-4752-AC0B-3DBB164C06FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D1A0A42-B51A-4848-A5E2-35D2BEEC5C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="500" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="199">
   <si>
     <t>AON PLC – DISCOUNTED CASH FLOW VALUATION</t>
   </si>
@@ -640,9 +640,6 @@
   </si>
   <si>
     <t>52-Week Trading Range</t>
-  </si>
-  <si>
-    <t>Note: Football field shows valuation range across methods. DCF Sensitivity uses WACC 8–12% and TGR 1.5–3.5% from Sensitivity sheet. Comps implied prices use FY2025E metrics. Current price ~$322 (June 2026).</t>
   </si>
 </sst>
 </file>
@@ -862,7 +859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -992,12 +989,6 @@
     <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1087,16 +1078,16 @@
     <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1213,7 +1204,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike" spc="-1">
+              <a:rPr lang="en-GB" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1339,10 +1330,10 @@
                   <c:v>184.36442151998091</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.472523364485985</c:v>
+                  <c:v>345.23738317757011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>370.09345794392522</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>305</c:v>
@@ -1456,10 +1447,10 @@
                   <c:v>268.25959227087219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2354392523364393</c:v>
+                  <c:v>9.3297196261681847</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>28.94953271028038</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>76</c:v>
@@ -1508,7 +1499,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr sz="1000" b="1" strike="noStrike" spc="-1">
+                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1893,16 +1884,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="94"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="95"/>
+      <c r="C4" s="91"/>
     </row>
     <row r="6" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
@@ -1924,7 +1915,7 @@
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="91">
+      <c r="C8" s="89">
         <v>46113</v>
       </c>
     </row>
@@ -3409,39 +3400,39 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="C4" s="52">
-        <f>(('FCF Build'!C10/(1+0.08)^1+'FCF Build'!D10/(1+0.08)^2+'FCF Build'!E10/(1+0.08)^3+'FCF Build'!F10/(1+0.08)^4+'FCF Build'!G10/(1+0.08)^5+('FCF Build'!G10*(1+0.015)/(0.08-0.015))/(1+0.08)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+C$3)^1+'FCF Build'!$D$10/(1+C$3)^2+'FCF Build'!$E$10/(1+C$3)^3+'FCF Build'!$F$10/(1+C$3)^4+'FCF Build'!$G$10/(1+C$3)^5+('FCF Build'!$G$10*(1+$B4)/(C$3-$B4))/(1+C$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>324.60184750018482</v>
       </c>
-      <c r="D4" s="53">
-        <f>(('FCF Build'!C10/(1+0.085)^1+'FCF Build'!D10/(1+0.085)^2+'FCF Build'!E10/(1+0.085)^3+'FCF Build'!F10/(1+0.085)^4+'FCF Build'!G10/(1+0.085)^5+('FCF Build'!G10*(1+0.015)/(0.085-0.015))/(1+0.085)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="D4" s="52">
+        <f>(('FCF Build'!$C$10/(1+D$3)^1+'FCF Build'!$D$10/(1+D$3)^2+'FCF Build'!$E$10/(1+D$3)^3+'FCF Build'!$F$10/(1+D$3)^4+'FCF Build'!$G$10/(1+D$3)^5+('FCF Build'!$G$10*(1+$B4)/(D$3-$B4))/(1+D$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>298.28385773515629</v>
       </c>
       <c r="E4" s="52">
-        <f>(('FCF Build'!C10/(1+0.09)^1+'FCF Build'!D10/(1+0.09)^2+'FCF Build'!E10/(1+0.09)^3+'FCF Build'!F10/(1+0.09)^4+'FCF Build'!G10/(1+0.09)^5+('FCF Build'!G10*(1+0.015)/(0.09-0.015))/(1+0.09)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+E$3)^1+'FCF Build'!$D$10/(1+E$3)^2+'FCF Build'!$E$10/(1+E$3)^3+'FCF Build'!$F$10/(1+E$3)^4+'FCF Build'!$G$10/(1+E$3)^5+('FCF Build'!$G$10*(1+$B4)/(E$3-$B4))/(1+E$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>275.48148924862426</v>
       </c>
-      <c r="F4" s="53">
-        <f>(('FCF Build'!C10/(1+0.095)^1+'FCF Build'!D10/(1+0.095)^2+'FCF Build'!E10/(1+0.095)^3+'FCF Build'!F10/(1+0.095)^4+'FCF Build'!G10/(1+0.095)^5+('FCF Build'!G10*(1+0.015)/(0.095-0.015))/(1+0.095)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="F4" s="52">
+        <f>(('FCF Build'!$C$10/(1+F$3)^1+'FCF Build'!$D$10/(1+F$3)^2+'FCF Build'!$E$10/(1+F$3)^3+'FCF Build'!$F$10/(1+F$3)^4+'FCF Build'!$G$10/(1+F$3)^5+('FCF Build'!$G$10*(1+$B4)/(F$3-$B4))/(1+F$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>255.53541897297333</v>
       </c>
       <c r="G4" s="52">
-        <f>(('FCF Build'!C10/(1+0.1)^1+'FCF Build'!D10/(1+0.1)^2+'FCF Build'!E10/(1+0.1)^3+'FCF Build'!F10/(1+0.1)^4+'FCF Build'!G10/(1+0.1)^5+('FCF Build'!G10*(1+0.015)/(0.1-0.015))/(1+0.1)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+G$3)^1+'FCF Build'!$D$10/(1+G$3)^2+'FCF Build'!$E$10/(1+G$3)^3+'FCF Build'!$F$10/(1+G$3)^4+'FCF Build'!$G$10/(1+G$3)^5+('FCF Build'!$G$10*(1+$B4)/(G$3-$B4))/(1+G$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>237.94146255638358</v>
       </c>
-      <c r="H4" s="53">
-        <f>(('FCF Build'!C10/(1+0.105)^1+'FCF Build'!D10/(1+0.105)^2+'FCF Build'!E10/(1+0.105)^3+'FCF Build'!F10/(1+0.105)^4+'FCF Build'!G10/(1+0.105)^5+('FCF Build'!G10*(1+0.015)/(0.105-0.015))/(1+0.105)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="H4" s="52">
+        <f>(('FCF Build'!$C$10/(1+H$3)^1+'FCF Build'!$D$10/(1+H$3)^2+'FCF Build'!$E$10/(1+H$3)^3+'FCF Build'!$F$10/(1+H$3)^4+'FCF Build'!$G$10/(1+H$3)^5+('FCF Build'!$G$10*(1+$B4)/(H$3-$B4))/(1+H$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>222.30748015266931</v>
       </c>
       <c r="I4" s="52">
-        <f>(('FCF Build'!C10/(1+0.11)^1+'FCF Build'!D10/(1+0.11)^2+'FCF Build'!E10/(1+0.11)^3+'FCF Build'!F10/(1+0.11)^4+'FCF Build'!G10/(1+0.11)^5+('FCF Build'!G10*(1+0.015)/(0.11-0.015))/(1+0.11)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+I$3)^1+'FCF Build'!$D$10/(1+I$3)^2+'FCF Build'!$E$10/(1+I$3)^3+'FCF Build'!$F$10/(1+I$3)^4+'FCF Build'!$G$10/(1+I$3)^5+('FCF Build'!$G$10*(1+$B4)/(I$3-$B4))/(1+I$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>208.3238909134835</v>
       </c>
-      <c r="J4" s="53">
-        <f>(('FCF Build'!C10/(1+0.115)^1+'FCF Build'!D10/(1+0.115)^2+'FCF Build'!E10/(1+0.115)^3+'FCF Build'!F10/(1+0.115)^4+'FCF Build'!G10/(1+0.115)^5+('FCF Build'!G10*(1+0.015)/(0.115-0.015))/(1+0.115)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="J4" s="52">
+        <f>(('FCF Build'!$C$10/(1+J$3)^1+'FCF Build'!$D$10/(1+J$3)^2+'FCF Build'!$E$10/(1+J$3)^3+'FCF Build'!$F$10/(1+J$3)^4+'FCF Build'!$G$10/(1+J$3)^5+('FCF Build'!$G$10*(1+$B4)/(J$3-$B4))/(1+J$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>195.74303313688517</v>
       </c>
       <c r="K4" s="52">
-        <f>(('FCF Build'!C10/(1+0.12)^1+'FCF Build'!D10/(1+0.12)^2+'FCF Build'!E10/(1+0.12)^3+'FCF Build'!F10/(1+0.12)^4+'FCF Build'!G10/(1+0.12)^5+('FCF Build'!G10*(1+0.015)/(0.12-0.015))/(1+0.12)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+K$3)^1+'FCF Build'!$D$10/(1+K$3)^2+'FCF Build'!$E$10/(1+K$3)^3+'FCF Build'!$F$10/(1+K$3)^4+'FCF Build'!$G$10/(1+K$3)^5+('FCF Build'!$G$10*(1+$B4)/(K$3-$B4))/(1+K$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>184.36442151998091</v>
       </c>
     </row>
@@ -3449,40 +3440,40 @@
       <c r="B5" s="51">
         <v>0.02</v>
       </c>
-      <c r="C5" s="53">
-        <f>(('FCF Build'!C10/(1+0.08)^1+'FCF Build'!D10/(1+0.08)^2+'FCF Build'!E10/(1+0.08)^3+'FCF Build'!F10/(1+0.08)^4+'FCF Build'!G10/(1+0.08)^5+('FCF Build'!G10*(1+0.02)/(0.08-0.02))/(1+0.08)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="C5" s="52">
+        <f>(('FCF Build'!$C$10/(1+C$3)^1+'FCF Build'!$D$10/(1+C$3)^2+'FCF Build'!$E$10/(1+C$3)^3+'FCF Build'!$F$10/(1+C$3)^4+'FCF Build'!$G$10/(1+C$3)^5+('FCF Build'!$G$10*(1+$B5)/(C$3-$B5))/(1+C$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>348.60600367968516</v>
       </c>
       <c r="D5" s="52">
-        <f>(('FCF Build'!C10/(1+0.085)^1+'FCF Build'!D10/(1+0.085)^2+'FCF Build'!E10/(1+0.085)^3+'FCF Build'!F10/(1+0.085)^4+'FCF Build'!G10/(1+0.085)^5+('FCF Build'!G10*(1+0.02)/(0.085-0.02))/(1+0.085)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+D$3)^1+'FCF Build'!$D$10/(1+D$3)^2+'FCF Build'!$E$10/(1+D$3)^3+'FCF Build'!$F$10/(1+D$3)^4+'FCF Build'!$G$10/(1+D$3)^5+('FCF Build'!$G$10*(1+$B5)/(D$3-$B5))/(1+D$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>318.48219982439031</v>
       </c>
-      <c r="E5" s="53">
-        <f>(('FCF Build'!C10/(1+0.09)^1+'FCF Build'!D10/(1+0.09)^2+'FCF Build'!E10/(1+0.09)^3+'FCF Build'!F10/(1+0.09)^4+'FCF Build'!G10/(1+0.09)^5+('FCF Build'!G10*(1+0.02)/(0.09-0.02))/(1+0.09)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="E5" s="52">
+        <f>(('FCF Build'!$C$10/(1+E$3)^1+'FCF Build'!$D$10/(1+E$3)^2+'FCF Build'!$E$10/(1+E$3)^3+'FCF Build'!$F$10/(1+E$3)^4+'FCF Build'!$G$10/(1+E$3)^5+('FCF Build'!$G$10*(1+$B5)/(E$3-$B5))/(1+E$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>292.66772550141616</v>
       </c>
       <c r="F5" s="52">
-        <f>(('FCF Build'!C10/(1+0.095)^1+'FCF Build'!D10/(1+0.095)^2+'FCF Build'!E10/(1+0.095)^3+'FCF Build'!F10/(1+0.095)^4+'FCF Build'!G10/(1+0.095)^5+('FCF Build'!G10*(1+0.02)/(0.095-0.02))/(1+0.095)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+F$3)^1+'FCF Build'!$D$10/(1+F$3)^2+'FCF Build'!$E$10/(1+F$3)^3+'FCF Build'!$F$10/(1+F$3)^4+'FCF Build'!$G$10/(1+F$3)^5+('FCF Build'!$G$10*(1+$B5)/(F$3-$B5))/(1+F$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>270.30058537078344</v>
       </c>
-      <c r="G5" s="53">
-        <f>(('FCF Build'!C10/(1+0.1)^1+'FCF Build'!D10/(1+0.1)^2+'FCF Build'!E10/(1+0.1)^3+'FCF Build'!F10/(1+0.1)^4+'FCF Build'!G10/(1+0.1)^5+('FCF Build'!G10*(1+0.02)/(0.1-0.02))/(1+0.1)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="G5" s="52">
+        <f>(('FCF Build'!$C$10/(1+G$3)^1+'FCF Build'!$D$10/(1+G$3)^2+'FCF Build'!$E$10/(1+G$3)^3+'FCF Build'!$F$10/(1+G$3)^4+'FCF Build'!$G$10/(1+G$3)^5+('FCF Build'!$G$10*(1+$B5)/(G$3-$B5))/(1+G$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>250.73428639090866</v>
       </c>
       <c r="H5" s="52">
-        <f>(('FCF Build'!C10/(1+0.105)^1+'FCF Build'!D10/(1+0.105)^2+'FCF Build'!E10/(1+0.105)^3+'FCF Build'!F10/(1+0.105)^4+'FCF Build'!G10/(1+0.105)^5+('FCF Build'!G10*(1+0.02)/(0.105-0.02))/(1+0.105)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+H$3)^1+'FCF Build'!$D$10/(1+H$3)^2+'FCF Build'!$E$10/(1+H$3)^3+'FCF Build'!$F$10/(1+H$3)^4+'FCF Build'!$G$10/(1+H$3)^5+('FCF Build'!$G$10*(1+$B5)/(H$3-$B5))/(1+H$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>233.47445468077174</v>
       </c>
-      <c r="I5" s="53">
-        <f>(('FCF Build'!C10/(1+0.11)^1+'FCF Build'!D10/(1+0.11)^2+'FCF Build'!E10/(1+0.11)^3+'FCF Build'!F10/(1+0.11)^4+'FCF Build'!G10/(1+0.11)^5+('FCF Build'!G10*(1+0.02)/(0.11-0.02))/(1+0.11)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="I5" s="52">
+        <f>(('FCF Build'!$C$10/(1+I$3)^1+'FCF Build'!$D$10/(1+I$3)^2+'FCF Build'!$E$10/(1+I$3)^3+'FCF Build'!$F$10/(1+I$3)^4+'FCF Build'!$G$10/(1+I$3)^5+('FCF Build'!$G$10*(1+$B5)/(I$3-$B5))/(1+I$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>218.13658009860799</v>
       </c>
       <c r="J5" s="52">
-        <f>(('FCF Build'!C10/(1+0.115)^1+'FCF Build'!D10/(1+0.115)^2+'FCF Build'!E10/(1+0.115)^3+'FCF Build'!F10/(1+0.115)^4+'FCF Build'!G10/(1+0.115)^5+('FCF Build'!G10*(1+0.02)/(0.115-0.02))/(1+0.115)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+J$3)^1+'FCF Build'!$D$10/(1+J$3)^2+'FCF Build'!$E$10/(1+J$3)^3+'FCF Build'!$F$10/(1+J$3)^4+'FCF Build'!$G$10/(1+J$3)^5+('FCF Build'!$G$10*(1+$B5)/(J$3-$B5))/(1+J$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>204.41710464141167</v>
       </c>
-      <c r="K5" s="53">
-        <f>(('FCF Build'!C10/(1+0.12)^1+'FCF Build'!D10/(1+0.12)^2+'FCF Build'!E10/(1+0.12)^3+'FCF Build'!F10/(1+0.12)^4+'FCF Build'!G10/(1+0.12)^5+('FCF Build'!G10*(1+0.02)/(0.12-0.02))/(1+0.12)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="K5" s="52">
+        <f>(('FCF Build'!$C$10/(1+K$3)^1+'FCF Build'!$D$10/(1+K$3)^2+'FCF Build'!$E$10/(1+K$3)^3+'FCF Build'!$F$10/(1+K$3)^4+'FCF Build'!$G$10/(1+K$3)^5+('FCF Build'!$G$10*(1+$B5)/(K$3-$B5))/(1+K$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>192.0731843278171</v>
       </c>
     </row>
@@ -3491,39 +3482,39 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C6" s="52">
-        <f>(('FCF Build'!C10/(1+0.08)^1+'FCF Build'!D10/(1+0.08)^2+'FCF Build'!E10/(1+0.08)^3+'FCF Build'!F10/(1+0.08)^4+'FCF Build'!G10/(1+0.08)^5+('FCF Build'!G10*(1+0.025)/(0.08-0.025))/(1+0.08)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+C$3)^1+'FCF Build'!$D$10/(1+C$3)^2+'FCF Build'!$E$10/(1+C$3)^3+'FCF Build'!$F$10/(1+C$3)^4+'FCF Build'!$G$10/(1+C$3)^5+('FCF Build'!$G$10*(1+$B6)/(C$3-$B6))/(1+C$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>376.97455189182182</v>
       </c>
-      <c r="D6" s="53">
-        <f>(('FCF Build'!C10/(1+0.085)^1+'FCF Build'!D10/(1+0.085)^2+'FCF Build'!E10/(1+0.085)^3+'FCF Build'!F10/(1+0.085)^4+'FCF Build'!G10/(1+0.085)^5+('FCF Build'!G10*(1+0.025)/(0.085-0.025))/(1+0.085)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="D6" s="52">
+        <f>(('FCF Build'!$C$10/(1+D$3)^1+'FCF Build'!$D$10/(1+D$3)^2+'FCF Build'!$E$10/(1+D$3)^3+'FCF Build'!$F$10/(1+D$3)^4+'FCF Build'!$G$10/(1+D$3)^5+('FCF Build'!$G$10*(1+$B6)/(D$3-$B6))/(1+D$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>342.04693226182997</v>
       </c>
-      <c r="E6" s="54">
-        <f>(('FCF Build'!C10/(1+0.09)^1+'FCF Build'!D10/(1+0.09)^2+'FCF Build'!E10/(1+0.09)^3+'FCF Build'!F10/(1+0.09)^4+'FCF Build'!G10/(1+0.09)^5+('FCF Build'!G10*(1+0.025)/(0.09-0.025))/(1+0.09)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="E6" s="52">
+        <f>(('FCF Build'!$C$10/(1+E$3)^1+'FCF Build'!$D$10/(1+E$3)^2+'FCF Build'!$E$10/(1+E$3)^3+'FCF Build'!$F$10/(1+E$3)^4+'FCF Build'!$G$10/(1+E$3)^5+('FCF Build'!$G$10*(1+$B6)/(E$3-$B6))/(1+E$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>312.49799810079139</v>
       </c>
-      <c r="F6" s="53">
-        <f>(('FCF Build'!C10/(1+0.095)^1+'FCF Build'!D10/(1+0.095)^2+'FCF Build'!E10/(1+0.095)^3+'FCF Build'!F10/(1+0.095)^4+'FCF Build'!G10/(1+0.095)^5+('FCF Build'!G10*(1+0.025)/(0.095-0.025))/(1+0.095)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="F6" s="52">
+        <f>(('FCF Build'!$C$10/(1+F$3)^1+'FCF Build'!$D$10/(1+F$3)^2+'FCF Build'!$E$10/(1+F$3)^3+'FCF Build'!$F$10/(1+F$3)^4+'FCF Build'!$G$10/(1+F$3)^5+('FCF Build'!$G$10*(1+$B6)/(F$3-$B6))/(1+F$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>287.17506125399478</v>
       </c>
       <c r="G6" s="52">
-        <f>(('FCF Build'!C10/(1+0.1)^1+'FCF Build'!D10/(1+0.1)^2+'FCF Build'!E10/(1+0.1)^3+'FCF Build'!F10/(1+0.1)^4+'FCF Build'!G10/(1+0.1)^5+('FCF Build'!G10*(1+0.025)/(0.1-0.025))/(1+0.1)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+G$3)^1+'FCF Build'!$D$10/(1+G$3)^2+'FCF Build'!$E$10/(1+G$3)^3+'FCF Build'!$F$10/(1+G$3)^4+'FCF Build'!$G$10/(1+G$3)^5+('FCF Build'!$G$10*(1+$B6)/(G$3-$B6))/(1+G$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>265.23282007003701</v>
       </c>
-      <c r="H6" s="53">
-        <f>(('FCF Build'!C10/(1+0.105)^1+'FCF Build'!D10/(1+0.105)^2+'FCF Build'!E10/(1+0.105)^3+'FCF Build'!F10/(1+0.105)^4+'FCF Build'!G10/(1+0.105)^5+('FCF Build'!G10*(1+0.025)/(0.105-0.025))/(1+0.105)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="H6" s="52">
+        <f>(('FCF Build'!$C$10/(1+H$3)^1+'FCF Build'!$D$10/(1+H$3)^2+'FCF Build'!$E$10/(1+H$3)^3+'FCF Build'!$F$10/(1+H$3)^4+'FCF Build'!$G$10/(1+H$3)^5+('FCF Build'!$G$10*(1+$B6)/(H$3-$B6))/(1+H$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>246.03730102488689</v>
       </c>
       <c r="I6" s="52">
-        <f>(('FCF Build'!C10/(1+0.11)^1+'FCF Build'!D10/(1+0.11)^2+'FCF Build'!E10/(1+0.11)^3+'FCF Build'!F10/(1+0.11)^4+'FCF Build'!G10/(1+0.11)^5+('FCF Build'!G10*(1+0.025)/(0.11-0.025))/(1+0.11)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+I$3)^1+'FCF Build'!$D$10/(1+I$3)^2+'FCF Build'!$E$10/(1+I$3)^3+'FCF Build'!$F$10/(1+I$3)^4+'FCF Build'!$G$10/(1+I$3)^5+('FCF Build'!$G$10*(1+$B6)/(I$3-$B6))/(1+I$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>229.10370330551177</v>
       </c>
-      <c r="J6" s="53">
-        <f>(('FCF Build'!C10/(1+0.115)^1+'FCF Build'!D10/(1+0.115)^2+'FCF Build'!E10/(1+0.115)^3+'FCF Build'!F10/(1+0.115)^4+'FCF Build'!G10/(1+0.115)^5+('FCF Build'!G10*(1+0.025)/(0.115-0.025))/(1+0.115)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="J6" s="52">
+        <f>(('FCF Build'!$C$10/(1+J$3)^1+'FCF Build'!$D$10/(1+J$3)^2+'FCF Build'!$E$10/(1+J$3)^3+'FCF Build'!$F$10/(1+J$3)^4+'FCF Build'!$G$10/(1+J$3)^5+('FCF Build'!$G$10*(1+$B6)/(J$3-$B6))/(1+J$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>214.05496186866327</v>
       </c>
       <c r="K6" s="52">
-        <f>(('FCF Build'!C10/(1+0.12)^1+'FCF Build'!D10/(1+0.12)^2+'FCF Build'!E10/(1+0.12)^3+'FCF Build'!F10/(1+0.12)^4+'FCF Build'!G10/(1+0.12)^5+('FCF Build'!G10*(1+0.025)/(0.12-0.025))/(1+0.12)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+K$3)^1+'FCF Build'!$D$10/(1+K$3)^2+'FCF Build'!$E$10/(1+K$3)^3+'FCF Build'!$F$10/(1+K$3)^4+'FCF Build'!$G$10/(1+K$3)^5+('FCF Build'!$G$10*(1+$B6)/(K$3-$B6))/(1+K$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>200.59339585226761</v>
       </c>
     </row>
@@ -3531,40 +3522,40 @@
       <c r="B7" s="51">
         <v>0.03</v>
       </c>
-      <c r="C7" s="53">
-        <f>(('FCF Build'!C10/(1+0.08)^1+'FCF Build'!D10/(1+0.08)^2+'FCF Build'!E10/(1+0.08)^3+'FCF Build'!F10/(1+0.08)^4+'FCF Build'!G10/(1+0.08)^5+('FCF Build'!G10*(1+0.03)/(0.08-0.03))/(1+0.08)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="C7" s="52">
+        <f>(('FCF Build'!$C$10/(1+C$3)^1+'FCF Build'!$D$10/(1+C$3)^2+'FCF Build'!$E$10/(1+C$3)^3+'FCF Build'!$F$10/(1+C$3)^4+'FCF Build'!$G$10/(1+C$3)^5+('FCF Build'!$G$10*(1+$B7)/(C$3-$B7))/(1+C$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>411.01680974638583</v>
       </c>
       <c r="D7" s="52">
-        <f>(('FCF Build'!C10/(1+0.085)^1+'FCF Build'!D10/(1+0.085)^2+'FCF Build'!E10/(1+0.085)^3+'FCF Build'!F10/(1+0.085)^4+'FCF Build'!G10/(1+0.085)^5+('FCF Build'!G10*(1+0.03)/(0.085-0.03))/(1+0.085)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+D$3)^1+'FCF Build'!$D$10/(1+D$3)^2+'FCF Build'!$E$10/(1+D$3)^3+'FCF Build'!$F$10/(1+D$3)^4+'FCF Build'!$G$10/(1+D$3)^5+('FCF Build'!$G$10*(1+$B7)/(D$3-$B7))/(1+D$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>369.89616150607685</v>
       </c>
-      <c r="E7" s="53">
-        <f>(('FCF Build'!C10/(1+0.09)^1+'FCF Build'!D10/(1+0.09)^2+'FCF Build'!E10/(1+0.09)^3+'FCF Build'!F10/(1+0.09)^4+'FCF Build'!G10/(1+0.09)^5+('FCF Build'!G10*(1+0.03)/(0.09-0.03))/(1+0.09)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="E7" s="52">
+        <f>(('FCF Build'!$C$10/(1+E$3)^1+'FCF Build'!$D$10/(1+E$3)^2+'FCF Build'!$E$10/(1+E$3)^3+'FCF Build'!$F$10/(1+E$3)^4+'FCF Build'!$G$10/(1+E$3)^5+('FCF Build'!$G$10*(1+$B7)/(E$3-$B7))/(1+E$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>335.63331613339597</v>
       </c>
       <c r="F7" s="52">
-        <f>(('FCF Build'!C10/(1+0.095)^1+'FCF Build'!D10/(1+0.095)^2+'FCF Build'!E10/(1+0.095)^3+'FCF Build'!F10/(1+0.095)^4+'FCF Build'!G10/(1+0.095)^5+('FCF Build'!G10*(1+0.03)/(0.095-0.03))/(1+0.095)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+F$3)^1+'FCF Build'!$D$10/(1+F$3)^2+'FCF Build'!$E$10/(1+F$3)^3+'FCF Build'!$F$10/(1+F$3)^4+'FCF Build'!$G$10/(1+F$3)^5+('FCF Build'!$G$10*(1+$B7)/(F$3-$B7))/(1+F$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>306.64561035000804</v>
       </c>
-      <c r="G7" s="53">
-        <f>(('FCF Build'!C10/(1+0.1)^1+'FCF Build'!D10/(1+0.1)^2+'FCF Build'!E10/(1+0.1)^3+'FCF Build'!F10/(1+0.1)^4+'FCF Build'!G10/(1+0.1)^5+('FCF Build'!G10*(1+0.03)/(0.1-0.03))/(1+0.1)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="G7" s="52">
+        <f>(('FCF Build'!$C$10/(1+G$3)^1+'FCF Build'!$D$10/(1+G$3)^2+'FCF Build'!$E$10/(1+G$3)^3+'FCF Build'!$F$10/(1+G$3)^4+'FCF Build'!$G$10/(1+G$3)^5+('FCF Build'!$G$10*(1+$B7)/(G$3-$B7))/(1+G$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>281.80257284618375</v>
       </c>
       <c r="H7" s="52">
-        <f>(('FCF Build'!C10/(1+0.105)^1+'FCF Build'!D10/(1+0.105)^2+'FCF Build'!E10/(1+0.105)^3+'FCF Build'!F10/(1+0.105)^4+'FCF Build'!G10/(1+0.105)^5+('FCF Build'!G10*(1+0.03)/(0.105-0.03))/(1+0.105)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+H$3)^1+'FCF Build'!$D$10/(1+H$3)^2+'FCF Build'!$E$10/(1+H$3)^3+'FCF Build'!$F$10/(1+H$3)^4+'FCF Build'!$G$10/(1+H$3)^5+('FCF Build'!$G$10*(1+$B7)/(H$3-$B7))/(1+H$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>260.27519354821743</v>
       </c>
-      <c r="I7" s="53">
-        <f>(('FCF Build'!C10/(1+0.11)^1+'FCF Build'!D10/(1+0.11)^2+'FCF Build'!E10/(1+0.11)^3+'FCF Build'!F10/(1+0.11)^4+'FCF Build'!G10/(1+0.11)^5+('FCF Build'!G10*(1+0.03)/(0.11-0.03))/(1+0.11)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="I7" s="52">
+        <f>(('FCF Build'!$C$10/(1+I$3)^1+'FCF Build'!$D$10/(1+I$3)^2+'FCF Build'!$E$10/(1+I$3)^3+'FCF Build'!$F$10/(1+I$3)^4+'FCF Build'!$G$10/(1+I$3)^5+('FCF Build'!$G$10*(1+$B7)/(I$3-$B7))/(1+I$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>241.44171691327858</v>
       </c>
       <c r="J7" s="52">
-        <f>(('FCF Build'!C10/(1+0.115)^1+'FCF Build'!D10/(1+0.115)^2+'FCF Build'!E10/(1+0.115)^3+'FCF Build'!F10/(1+0.115)^4+'FCF Build'!G10/(1+0.115)^5+('FCF Build'!G10*(1+0.03)/(0.115-0.03))/(1+0.115)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+J$3)^1+'FCF Build'!$D$10/(1+J$3)^2+'FCF Build'!$E$10/(1+J$3)^3+'FCF Build'!$F$10/(1+J$3)^4+'FCF Build'!$G$10/(1+J$3)^5+('FCF Build'!$G$10*(1+$B7)/(J$3-$B7))/(1+J$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>224.82668465206211</v>
       </c>
-      <c r="K7" s="53">
-        <f>(('FCF Build'!C10/(1+0.12)^1+'FCF Build'!D10/(1+0.12)^2+'FCF Build'!E10/(1+0.12)^3+'FCF Build'!F10/(1+0.12)^4+'FCF Build'!G10/(1+0.12)^5+('FCF Build'!G10*(1+0.03)/(0.12-0.03))/(1+0.12)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="K7" s="52">
+        <f>(('FCF Build'!$C$10/(1+K$3)^1+'FCF Build'!$D$10/(1+K$3)^2+'FCF Build'!$E$10/(1+K$3)^3+'FCF Build'!$F$10/(1+K$3)^4+'FCF Build'!$G$10/(1+K$3)^5+('FCF Build'!$G$10*(1+$B7)/(K$3-$B7))/(1+K$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>210.06029754610154</v>
       </c>
     </row>
@@ -3573,52 +3564,52 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C8" s="52">
-        <f>(('FCF Build'!C10/(1+0.08)^1+'FCF Build'!D10/(1+0.08)^2+'FCF Build'!E10/(1+0.08)^3+'FCF Build'!F10/(1+0.08)^4+'FCF Build'!G10/(1+0.08)^5+('FCF Build'!G10*(1+0.035)/(0.08-0.035))/(1+0.08)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+C$3)^1+'FCF Build'!$D$10/(1+C$3)^2+'FCF Build'!$E$10/(1+C$3)^3+'FCF Build'!$F$10/(1+C$3)^4+'FCF Build'!$G$10/(1+C$3)^5+('FCF Build'!$G$10*(1+$B8)/(C$3-$B8))/(1+C$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>452.6240137908531</v>
       </c>
-      <c r="D8" s="53">
-        <f>(('FCF Build'!C10/(1+0.085)^1+'FCF Build'!D10/(1+0.085)^2+'FCF Build'!E10/(1+0.085)^3+'FCF Build'!F10/(1+0.085)^4+'FCF Build'!G10/(1+0.085)^5+('FCF Build'!G10*(1+0.035)/(0.085-0.035))/(1+0.085)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="D8" s="52">
+        <f>(('FCF Build'!$C$10/(1+D$3)^1+'FCF Build'!$D$10/(1+D$3)^2+'FCF Build'!$E$10/(1+D$3)^3+'FCF Build'!$F$10/(1+D$3)^4+'FCF Build'!$G$10/(1+D$3)^5+('FCF Build'!$G$10*(1+$B8)/(D$3-$B8))/(1+D$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>403.3152365991732</v>
       </c>
       <c r="E8" s="52">
-        <f>(('FCF Build'!C10/(1+0.09)^1+'FCF Build'!D10/(1+0.09)^2+'FCF Build'!E10/(1+0.09)^3+'FCF Build'!F10/(1+0.09)^4+'FCF Build'!G10/(1+0.09)^5+('FCF Build'!G10*(1+0.035)/(0.09-0.035))/(1+0.09)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+E$3)^1+'FCF Build'!$D$10/(1+E$3)^2+'FCF Build'!$E$10/(1+E$3)^3+'FCF Build'!$F$10/(1+E$3)^4+'FCF Build'!$G$10/(1+E$3)^5+('FCF Build'!$G$10*(1+$B8)/(E$3-$B8))/(1+E$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>362.9750556264741</v>
       </c>
-      <c r="F8" s="53">
-        <f>(('FCF Build'!C10/(1+0.095)^1+'FCF Build'!D10/(1+0.095)^2+'FCF Build'!E10/(1+0.095)^3+'FCF Build'!F10/(1+0.095)^4+'FCF Build'!G10/(1+0.095)^5+('FCF Build'!G10*(1+0.035)/(0.095-0.035))/(1+0.095)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="F8" s="52">
+        <f>(('FCF Build'!$C$10/(1+F$3)^1+'FCF Build'!$D$10/(1+F$3)^2+'FCF Build'!$E$10/(1+F$3)^3+'FCF Build'!$F$10/(1+F$3)^4+'FCF Build'!$G$10/(1+F$3)^5+('FCF Build'!$G$10*(1+$B8)/(F$3-$B8))/(1+F$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>329.36125096202346</v>
       </c>
       <c r="G8" s="52">
-        <f>(('FCF Build'!C10/(1+0.1)^1+'FCF Build'!D10/(1+0.1)^2+'FCF Build'!E10/(1+0.1)^3+'FCF Build'!F10/(1+0.1)^4+'FCF Build'!G10/(1+0.1)^5+('FCF Build'!G10*(1+0.035)/(0.1-0.035))/(1+0.1)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+G$3)^1+'FCF Build'!$D$10/(1+G$3)^2+'FCF Build'!$E$10/(1+G$3)^3+'FCF Build'!$F$10/(1+G$3)^4+'FCF Build'!$G$10/(1+G$3)^5+('FCF Build'!$G$10*(1+$B8)/(G$3-$B8))/(1+G$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>300.9215183571223</v>
       </c>
-      <c r="H8" s="53">
-        <f>(('FCF Build'!C10/(1+0.105)^1+'FCF Build'!D10/(1+0.105)^2+'FCF Build'!E10/(1+0.105)^3+'FCF Build'!F10/(1+0.105)^4+'FCF Build'!G10/(1+0.105)^5+('FCF Build'!G10*(1+0.035)/(0.105-0.035))/(1+0.105)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="H8" s="52">
+        <f>(('FCF Build'!$C$10/(1+H$3)^1+'FCF Build'!$D$10/(1+H$3)^2+'FCF Build'!$E$10/(1+H$3)^3+'FCF Build'!$F$10/(1+H$3)^4+'FCF Build'!$G$10/(1+H$3)^5+('FCF Build'!$G$10*(1+$B8)/(H$3-$B8))/(1+H$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>276.54707071773805</v>
       </c>
       <c r="I8" s="52">
-        <f>(('FCF Build'!C10/(1+0.11)^1+'FCF Build'!D10/(1+0.11)^2+'FCF Build'!E10/(1+0.11)^3+'FCF Build'!F10/(1+0.11)^4+'FCF Build'!G10/(1+0.11)^5+('FCF Build'!G10*(1+0.035)/(0.11-0.035))/(1+0.11)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+I$3)^1+'FCF Build'!$D$10/(1+I$3)^2+'FCF Build'!$E$10/(1+I$3)^3+'FCF Build'!$F$10/(1+I$3)^4+'FCF Build'!$G$10/(1+I$3)^5+('FCF Build'!$G$10*(1+$B8)/(I$3-$B8))/(1+I$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>255.42479900208093</v>
       </c>
-      <c r="J8" s="53">
-        <f>(('FCF Build'!C10/(1+0.115)^1+'FCF Build'!D10/(1+0.115)^2+'FCF Build'!E10/(1+0.115)^3+'FCF Build'!F10/(1+0.115)^4+'FCF Build'!G10/(1+0.115)^5+('FCF Build'!G10*(1+0.035)/(0.115-0.035))/(1+0.115)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+      <c r="J8" s="52">
+        <f>(('FCF Build'!$C$10/(1+J$3)^1+'FCF Build'!$D$10/(1+J$3)^2+'FCF Build'!$E$10/(1+J$3)^3+'FCF Build'!$F$10/(1+J$3)^4+'FCF Build'!$G$10/(1+J$3)^5+('FCF Build'!$G$10*(1+$B8)/(J$3-$B8))/(1+J$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>236.94487278338582</v>
       </c>
       <c r="K8" s="52">
-        <f>(('FCF Build'!C10/(1+0.12)^1+'FCF Build'!D10/(1+0.12)^2+'FCF Build'!E10/(1+0.12)^3+'FCF Build'!F10/(1+0.12)^4+'FCF Build'!G10/(1+0.12)^5+('FCF Build'!G10*(1+0.035)/(0.12-0.035))/(1+0.12)^5)-'DCF Valuation'!C24-'DCF Valuation'!C25)/'DCF Valuation'!C27</f>
+        <f>(('FCF Build'!$C$10/(1+K$3)^1+'FCF Build'!$D$10/(1+K$3)^2+'FCF Build'!$E$10/(1+K$3)^3+'FCF Build'!$F$10/(1+K$3)^4+'FCF Build'!$G$10/(1+K$3)^5+('FCF Build'!$G$10*(1+$B8)/(K$3-$B8))/(1+K$3)^5)-'DCF Valuation'!$C$24-'DCF Valuation'!$C$25)/'DCF Valuation'!$C$27</f>
         <v>220.64095238038652</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="94" t="s">
         <v>138</v>
       </c>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3713,32 +3704,32 @@
       <c r="B5" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="53">
         <v>88000</v>
       </c>
-      <c r="D5" s="55">
+      <c r="D5" s="53">
         <v>5800</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="53">
         <f t="shared" ref="E5:E10" si="0">C5+D5</f>
         <v>93800</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="54">
         <v>18.5</v>
       </c>
-      <c r="G5" s="56">
+      <c r="G5" s="54">
         <v>17.2</v>
       </c>
-      <c r="H5" s="56">
+      <c r="H5" s="54">
         <v>16</v>
       </c>
-      <c r="I5" s="56">
+      <c r="I5" s="54">
         <v>27.5</v>
       </c>
-      <c r="J5" s="56">
+      <c r="J5" s="54">
         <v>25.2</v>
       </c>
-      <c r="K5" s="56">
+      <c r="K5" s="54">
         <v>23.1</v>
       </c>
     </row>
@@ -3746,32 +3737,32 @@
       <c r="B6" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="55">
         <v>30500</v>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="55">
         <v>4500</v>
       </c>
-      <c r="E6" s="57">
+      <c r="E6" s="55">
         <f t="shared" si="0"/>
         <v>35000</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="56">
         <v>13</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="56">
         <v>12.2</v>
       </c>
-      <c r="H6" s="58">
+      <c r="H6" s="56">
         <v>11.5</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="56">
         <v>19.8</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="56">
         <v>18.2</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="56">
         <v>16.8</v>
       </c>
     </row>
@@ -3779,32 +3770,32 @@
       <c r="B7" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="53">
         <v>58000</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="53">
         <v>8800</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="53">
         <f t="shared" si="0"/>
         <v>66800</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="54">
         <v>17</v>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="54">
         <v>15.8</v>
       </c>
-      <c r="H7" s="56">
+      <c r="H7" s="54">
         <v>14.7</v>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="54">
         <v>32.5</v>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="54">
         <v>29.8</v>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="54">
         <v>27.2</v>
       </c>
     </row>
@@ -3812,32 +3803,32 @@
       <c r="B8" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="55">
         <v>12500</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="55">
         <v>2300</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="55">
         <f t="shared" si="0"/>
         <v>14800</v>
       </c>
-      <c r="F8" s="58">
+      <c r="F8" s="56">
         <v>14.8</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8" s="56">
         <v>13.6</v>
       </c>
-      <c r="H8" s="58">
+      <c r="H8" s="56">
         <v>12.6</v>
       </c>
-      <c r="I8" s="58">
+      <c r="I8" s="56">
         <v>22.5</v>
       </c>
-      <c r="J8" s="58">
+      <c r="J8" s="56">
         <v>20.5</v>
       </c>
-      <c r="K8" s="58">
+      <c r="K8" s="56">
         <v>18.8</v>
       </c>
     </row>
@@ -3845,32 +3836,32 @@
       <c r="B9" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="53">
         <v>10000</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="53">
         <v>900</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="53">
         <f t="shared" si="0"/>
         <v>10900</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="54">
         <v>12.5</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="54">
         <v>11.6</v>
       </c>
-      <c r="H9" s="56">
+      <c r="H9" s="54">
         <v>10.8</v>
       </c>
-      <c r="I9" s="56">
+      <c r="I9" s="54">
         <v>19</v>
       </c>
-      <c r="J9" s="56">
+      <c r="J9" s="54">
         <v>17.5</v>
       </c>
-      <c r="K9" s="56">
+      <c r="K9" s="54">
         <v>16.2</v>
       </c>
     </row>
@@ -3878,32 +3869,32 @@
       <c r="B10" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="57">
         <v>68900</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="57">
         <v>8200</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="57">
         <f t="shared" si="0"/>
         <v>77100</v>
       </c>
-      <c r="F10" s="60">
+      <c r="F10" s="58">
         <v>16.2</v>
       </c>
-      <c r="G10" s="60">
+      <c r="G10" s="58">
         <v>15.1</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="58">
         <v>14.1</v>
       </c>
-      <c r="I10" s="60">
+      <c r="I10" s="58">
         <v>24.8</v>
       </c>
-      <c r="J10" s="60">
+      <c r="J10" s="58">
         <v>22.6</v>
       </c>
-      <c r="K10" s="60">
+      <c r="K10" s="58">
         <v>20.8</v>
       </c>
     </row>
@@ -3954,33 +3945,33 @@
       </c>
     </row>
     <row r="14" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="63">
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61">
         <f t="shared" ref="F14:K14" si="1">AVERAGE(F5:F9)</f>
         <v>15.16</v>
       </c>
-      <c r="G14" s="63">
+      <c r="G14" s="61">
         <f t="shared" si="1"/>
         <v>14.080000000000002</v>
       </c>
-      <c r="H14" s="63">
+      <c r="H14" s="61">
         <f t="shared" si="1"/>
         <v>13.120000000000001</v>
       </c>
-      <c r="I14" s="63">
+      <c r="I14" s="61">
         <f t="shared" si="1"/>
         <v>24.259999999999998</v>
       </c>
-      <c r="J14" s="63">
+      <c r="J14" s="61">
         <f t="shared" si="1"/>
         <v>22.240000000000002</v>
       </c>
-      <c r="K14" s="63">
+      <c r="K14" s="61">
         <f t="shared" si="1"/>
         <v>20.420000000000002</v>
       </c>
@@ -3989,62 +3980,62 @@
       <c r="B15" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="65">
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="63">
         <f t="shared" ref="F15:K15" si="2">MEDIAN(F5:F9)</f>
         <v>14.8</v>
       </c>
-      <c r="G15" s="65">
+      <c r="G15" s="63">
         <f t="shared" si="2"/>
         <v>13.6</v>
       </c>
-      <c r="H15" s="65">
+      <c r="H15" s="63">
         <f t="shared" si="2"/>
         <v>12.6</v>
       </c>
-      <c r="I15" s="65">
+      <c r="I15" s="63">
         <f t="shared" si="2"/>
         <v>22.5</v>
       </c>
-      <c r="J15" s="65">
+      <c r="J15" s="63">
         <f t="shared" si="2"/>
         <v>20.5</v>
       </c>
-      <c r="K15" s="65">
+      <c r="K15" s="63">
         <f t="shared" si="2"/>
         <v>18.8</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63">
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="61">
         <f t="shared" ref="F16:K16" si="3">MIN(F5:F9)</f>
         <v>12.5</v>
       </c>
-      <c r="G16" s="63">
+      <c r="G16" s="61">
         <f t="shared" si="3"/>
         <v>11.6</v>
       </c>
-      <c r="H16" s="63">
+      <c r="H16" s="61">
         <f t="shared" si="3"/>
         <v>10.8</v>
       </c>
-      <c r="I16" s="63">
+      <c r="I16" s="61">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="J16" s="63">
+      <c r="J16" s="61">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
-      <c r="K16" s="63">
+      <c r="K16" s="61">
         <f t="shared" si="3"/>
         <v>16.2</v>
       </c>
@@ -4053,62 +4044,62 @@
       <c r="B17" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="65">
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="63">
         <f t="shared" ref="F17:K17" si="4">MAX(F5:F9)</f>
         <v>18.5</v>
       </c>
-      <c r="G17" s="65">
+      <c r="G17" s="63">
         <f t="shared" si="4"/>
         <v>17.2</v>
       </c>
-      <c r="H17" s="65">
+      <c r="H17" s="63">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="I17" s="65">
+      <c r="I17" s="63">
         <f t="shared" si="4"/>
         <v>32.5</v>
       </c>
-      <c r="J17" s="65">
+      <c r="J17" s="63">
         <f t="shared" si="4"/>
         <v>29.8</v>
       </c>
-      <c r="K17" s="65">
+      <c r="K17" s="63">
         <f t="shared" si="4"/>
         <v>27.2</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="63">
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="61">
         <f t="shared" ref="F18:K18" si="5">PERCENTILE(F5:F9,0.25)</f>
         <v>13</v>
       </c>
-      <c r="G18" s="63">
+      <c r="G18" s="61">
         <f t="shared" si="5"/>
         <v>12.2</v>
       </c>
-      <c r="H18" s="63">
+      <c r="H18" s="61">
         <f t="shared" si="5"/>
         <v>11.5</v>
       </c>
-      <c r="I18" s="63">
+      <c r="I18" s="61">
         <f t="shared" si="5"/>
         <v>19.8</v>
       </c>
-      <c r="J18" s="63">
+      <c r="J18" s="61">
         <f t="shared" si="5"/>
         <v>18.2</v>
       </c>
-      <c r="K18" s="63">
+      <c r="K18" s="61">
         <f t="shared" si="5"/>
         <v>16.8</v>
       </c>
@@ -4117,30 +4108,30 @@
       <c r="B19" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="65">
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="63">
         <f t="shared" ref="F19:K19" si="6">PERCENTILE(F5:F9,0.75)</f>
         <v>17</v>
       </c>
-      <c r="G19" s="65">
+      <c r="G19" s="63">
         <f t="shared" si="6"/>
         <v>15.8</v>
       </c>
-      <c r="H19" s="65">
+      <c r="H19" s="63">
         <f t="shared" si="6"/>
         <v>14.7</v>
       </c>
-      <c r="I19" s="65">
+      <c r="I19" s="63">
         <f t="shared" si="6"/>
         <v>27.5</v>
       </c>
-      <c r="J19" s="65">
+      <c r="J19" s="63">
         <f t="shared" si="6"/>
         <v>25.2</v>
       </c>
-      <c r="K19" s="65">
+      <c r="K19" s="63">
         <f t="shared" si="6"/>
         <v>23.1</v>
       </c>
@@ -4191,151 +4182,151 @@
       <c r="B24" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="C24" s="66">
+      <c r="C24" s="64">
         <f>F14</f>
         <v>15.16</v>
       </c>
-      <c r="D24" s="67">
-        <f>'Income Statement'!F8</f>
-        <v>734.4</v>
-      </c>
-      <c r="E24" s="55">
+      <c r="D24" s="65">
+        <f>'Income Statement'!E5</f>
+        <v>5546</v>
+      </c>
+      <c r="E24" s="53">
         <f>C24*D24</f>
-        <v>11133.503999999999</v>
-      </c>
-      <c r="F24" s="68">
+        <v>84077.36</v>
+      </c>
+      <c r="F24" s="66">
         <f>'DCF Valuation'!C24</f>
         <v>8200</v>
       </c>
-      <c r="G24" s="69">
+      <c r="G24" s="67">
         <f>E24-F24</f>
-        <v>2933.503999999999</v>
-      </c>
-      <c r="H24" s="68">
+        <v>75877.36</v>
+      </c>
+      <c r="H24" s="66">
         <f>'DCF Valuation'!C27</f>
         <v>214</v>
       </c>
-      <c r="I24" s="70">
+      <c r="I24" s="68">
         <f>G24/H24</f>
-        <v>13.707962616822424</v>
-      </c>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+        <v>354.56710280373829</v>
+      </c>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
     </row>
     <row r="25" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="C25" s="71">
+      <c r="C25" s="69">
         <f>F15</f>
         <v>14.8</v>
       </c>
       <c r="D25" s="36">
-        <f>'Income Statement'!F8</f>
-        <v>734.4</v>
-      </c>
-      <c r="E25" s="57">
+        <f>'Income Statement'!E5</f>
+        <v>5546</v>
+      </c>
+      <c r="E25" s="55">
         <f>C25*D25</f>
-        <v>10869.12</v>
-      </c>
-      <c r="F25" s="72">
+        <v>82080.800000000003</v>
+      </c>
+      <c r="F25" s="70">
         <f>'DCF Valuation'!C24</f>
         <v>8200</v>
       </c>
-      <c r="G25" s="73">
+      <c r="G25" s="71">
         <f>E25-F25</f>
-        <v>2669.1200000000008</v>
-      </c>
-      <c r="H25" s="72">
+        <v>73880.800000000003</v>
+      </c>
+      <c r="H25" s="70">
         <f>'DCF Valuation'!C27</f>
         <v>214</v>
       </c>
-      <c r="I25" s="70">
+      <c r="I25" s="68">
         <f>G25/H25</f>
-        <v>12.472523364485985</v>
-      </c>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
+        <v>345.23738317757011</v>
+      </c>
+      <c r="J25" s="62"/>
+      <c r="K25" s="62"/>
     </row>
     <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="C26" s="66">
+      <c r="C26" s="64">
         <f>I14</f>
         <v>24.259999999999998</v>
       </c>
-      <c r="D26" s="67">
-        <f>'Income Statement'!F12</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="74" t="s">
+      <c r="D26" s="65">
+        <f>'Income Statement'!E11</f>
+        <v>3520</v>
+      </c>
+      <c r="E26" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="F26" s="74" t="s">
+      <c r="F26" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="G26" s="69">
+      <c r="G26" s="67">
         <f>C26*D26</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="68">
+        <v>85395.199999999997</v>
+      </c>
+      <c r="H26" s="66">
         <f>'DCF Valuation'!C27</f>
         <v>214</v>
       </c>
-      <c r="I26" s="70">
+      <c r="I26" s="68">
         <f>G26/H26</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+        <v>399.0429906542056</v>
+      </c>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="71">
+      <c r="C27" s="69">
         <f>I15</f>
         <v>22.5</v>
       </c>
       <c r="D27" s="36">
-        <f>'Income Statement'!F12</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="75" t="s">
+        <f>'Income Statement'!E11</f>
+        <v>3520</v>
+      </c>
+      <c r="E27" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="F27" s="75" t="s">
+      <c r="F27" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="G27" s="73">
+      <c r="G27" s="71">
         <f>C27*D27</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="72">
+        <v>79200</v>
+      </c>
+      <c r="H27" s="70">
         <f>'DCF Valuation'!C27</f>
         <v>214</v>
       </c>
-      <c r="I27" s="70">
+      <c r="I27" s="68">
         <f>G27/H27</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="64"/>
-      <c r="K27" s="64"/>
+        <v>370.09345794392522</v>
+      </c>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
     </row>
     <row r="29" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="97" t="s">
+      <c r="B29" s="95" t="s">
         <v>184</v>
       </c>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="97"/>
-      <c r="G29" s="97"/>
-      <c r="H29" s="97"/>
-      <c r="I29" s="97"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="95"/>
+      <c r="H29" s="95"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4409,15 +4400,15 @@
         <f t="shared" ref="I3:J7" si="0">B4</f>
         <v>DCF – Base Case</v>
       </c>
-      <c r="J3" s="76">
+      <c r="J3" s="74">
         <f t="shared" si="0"/>
         <v>388.96410195193073</v>
       </c>
-      <c r="K3" s="76">
+      <c r="K3" s="74">
         <f>E4-C4</f>
         <v>0</v>
       </c>
-      <c r="L3" s="76">
+      <c r="L3" s="74">
         <f>D4</f>
         <v>388.96410195193073</v>
       </c>
@@ -4426,19 +4417,19 @@
       <c r="B4" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="77">
+      <c r="C4" s="75">
         <f>'DCF Valuation'!C28</f>
         <v>388.96410195193073</v>
       </c>
-      <c r="D4" s="78">
+      <c r="D4" s="76">
         <f>'DCF Valuation'!C28</f>
         <v>388.96410195193073</v>
       </c>
-      <c r="E4" s="77">
+      <c r="E4" s="75">
         <f>'DCF Valuation'!C28</f>
         <v>388.96410195193073</v>
       </c>
-      <c r="F4" s="79">
+      <c r="F4" s="77">
         <f>'DCF Valuation'!C29</f>
         <v>322</v>
       </c>
@@ -4446,36 +4437,36 @@
         <f t="shared" si="0"/>
         <v>DCF – Sensitivity Range</v>
       </c>
-      <c r="J4" s="76">
+      <c r="J4" s="74">
         <f t="shared" si="0"/>
         <v>184.36442151998091</v>
       </c>
-      <c r="K4" s="76">
+      <c r="K4" s="74">
         <f>E5-C5</f>
         <v>268.25959227087219</v>
       </c>
-      <c r="L4" s="76">
+      <c r="L4" s="74">
         <f>D5</f>
         <v>388.96410195193073</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="80">
+      <c r="C5" s="78">
         <f>Sensitivity!K4</f>
         <v>184.36442151998091</v>
       </c>
-      <c r="D5" s="81">
+      <c r="D5" s="79">
         <f>'DCF Valuation'!C28</f>
         <v>388.96410195193073</v>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="78">
         <f>Sensitivity!C8</f>
         <v>452.6240137908531</v>
       </c>
-      <c r="F5" s="82">
+      <c r="F5" s="80">
         <f>'DCF Valuation'!C29</f>
         <v>322</v>
       </c>
@@ -4483,36 +4474,36 @@
         <f t="shared" si="0"/>
         <v>EV/EBITDA Comps</v>
       </c>
-      <c r="J5" s="76">
+      <c r="J5" s="74">
         <f t="shared" si="0"/>
-        <v>12.472523364485985</v>
-      </c>
-      <c r="K5" s="76">
+        <v>345.23738317757011</v>
+      </c>
+      <c r="K5" s="74">
         <f>E6-C6</f>
-        <v>1.2354392523364393</v>
-      </c>
-      <c r="L5" s="76">
+        <v>9.3297196261681847</v>
+      </c>
+      <c r="L5" s="74">
         <f>D6</f>
-        <v>13.090242990654204</v>
+        <v>349.9022429906542</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="81" t="s">
         <v>196</v>
       </c>
-      <c r="C6" s="84">
+      <c r="C6" s="82">
         <f>MIN('Trading Comps'!I24,'Trading Comps'!I25)</f>
-        <v>12.472523364485985</v>
-      </c>
-      <c r="D6" s="85">
+        <v>345.23738317757011</v>
+      </c>
+      <c r="D6" s="83">
         <f>AVERAGE('Trading Comps'!I24,'Trading Comps'!I25)</f>
-        <v>13.090242990654204</v>
-      </c>
-      <c r="E6" s="84">
+        <v>349.9022429906542</v>
+      </c>
+      <c r="E6" s="82">
         <f>MAX('Trading Comps'!I24,'Trading Comps'!I25)</f>
-        <v>13.707962616822424</v>
-      </c>
-      <c r="F6" s="86">
+        <v>354.56710280373829</v>
+      </c>
+      <c r="F6" s="84">
         <f>'DCF Valuation'!C29</f>
         <v>322</v>
       </c>
@@ -4520,36 +4511,36 @@
         <f t="shared" si="0"/>
         <v>P/E Comps</v>
       </c>
-      <c r="J6" s="76">
+      <c r="J6" s="74">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="76">
+        <v>370.09345794392522</v>
+      </c>
+      <c r="K6" s="74">
         <f>E7-C7</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="76">
+        <v>28.94953271028038</v>
+      </c>
+      <c r="L6" s="74">
         <f>D7</f>
-        <v>0</v>
+        <v>384.56822429906538</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="81" t="s">
         <v>197</v>
       </c>
-      <c r="C7" s="84">
+      <c r="C7" s="82">
         <f>MIN('Trading Comps'!I26,'Trading Comps'!I27)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="85">
+        <v>370.09345794392522</v>
+      </c>
+      <c r="D7" s="83">
         <f>AVERAGE('Trading Comps'!I26,'Trading Comps'!I27)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="84">
+        <v>384.56822429906538</v>
+      </c>
+      <c r="E7" s="82">
         <f>MAX('Trading Comps'!I26,'Trading Comps'!I27)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="86">
+        <v>399.0429906542056</v>
+      </c>
+      <c r="F7" s="84">
         <f>'DCF Valuation'!C29</f>
         <v>322</v>
       </c>
@@ -4557,44 +4548,42 @@
         <f t="shared" si="0"/>
         <v>52-Week Trading Range</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="74">
         <f t="shared" si="0"/>
         <v>305</v>
       </c>
-      <c r="K7" s="76">
+      <c r="K7" s="74">
         <f>E8-C8</f>
         <v>76</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="74">
         <f>D8</f>
         <v>343</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="85" t="s">
         <v>198</v>
       </c>
-      <c r="C8" s="88">
+      <c r="C8" s="86">
         <v>305</v>
       </c>
-      <c r="D8" s="89">
+      <c r="D8" s="87">
         <v>343</v>
       </c>
-      <c r="E8" s="88">
+      <c r="E8" s="86">
         <v>381</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="88">
         <f>'DCF Valuation'!C29</f>
         <v>322</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I10" s="98" t="s">
-        <v>199</v>
-      </c>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
-      <c r="L10" s="98"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="2">
